--- a/sorting_sahayak/assets/samples/template_scheme.xlsx
+++ b/sorting_sahayak/assets/samples/template_scheme.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="32">
   <si>
     <t xml:space="preserve">Type</t>
   </si>
@@ -67,31 +67,37 @@
     <t xml:space="preserve">Bag 12</t>
   </si>
   <si>
-    <t xml:space="preserve">Puttur SO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A</t>
+    <t xml:space="preserve">Puttur Line</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12</t>
   </si>
   <si>
     <t xml:space="preserve">example row – delete</t>
   </si>
   <si>
+    <t xml:space="preserve">TD</t>
+  </si>
+  <si>
     <t xml:space="preserve">#D32F2F</t>
   </si>
   <si>
-    <t xml:space="preserve">Range</t>
-  </si>
-  <si>
-    <t xml:space="preserve">574299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bag 02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mangaluru NSH</t>
+    <t xml:space="preserve">Sampaje</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">560</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BANGALORE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Karnataka</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Non-TD</t>
   </si>
   <si>
     <t xml:space="preserve">Default</t>
@@ -429,33 +435,33 @@
         <v>20</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="N2" s="1" t="s">
         <v>16</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>16</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>23</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>16</v>
       </c>
       <c r="G3" s="1" t="s">
         <v>16</v>
@@ -467,16 +473,16 @@
         <v>17</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="L3" s="1" t="s">
         <v>20</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="N3" s="1" t="s">
         <v>16</v>
@@ -499,7 +505,7 @@
         <v>16</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>16</v>
@@ -511,10 +517,10 @@
         <v>16</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K4" s="1" t="s">
         <v>16</v>
@@ -523,7 +529,7 @@
         <v>20</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="N4" s="1" t="s">
         <v>16</v>
@@ -534,7 +540,7 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>16</v>
@@ -558,10 +564,10 @@
         <v>16</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="K5" s="1" t="s">
         <v>16</v>
@@ -570,7 +576,7 @@
         <v>20</v>
       </c>
       <c r="M5" s="1" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="N5" s="1" t="s">
         <v>16</v>
